--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.30446082503026</v>
+        <v>2.161974884067417</v>
       </c>
       <c r="D2" t="n">
-        <v>5.412473486685798</v>
+        <v>0.8795269415864422</v>
       </c>
       <c r="E2" t="n">
-        <v>6.923154521083188</v>
+        <v>1.125012609676018</v>
       </c>
       <c r="F2" t="n">
-        <v>9.024405486930508</v>
+        <v>1.466465891626208</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.572189016578012</v>
+        <v>0.9054807151939269</v>
       </c>
       <c r="D3" t="n">
-        <v>10.50975978689325</v>
+        <v>1.707835965370153</v>
       </c>
       <c r="E3" t="n">
-        <v>6.923154521083188</v>
+        <v>1.125012609676018</v>
       </c>
       <c r="F3" t="n">
-        <v>9.024405486930508</v>
+        <v>1.466465891626208</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.92783023073195</v>
+        <v>4.050772412493941</v>
       </c>
       <c r="D4" t="n">
-        <v>26.96548647350784</v>
+        <v>4.381891551945023</v>
       </c>
       <c r="E4" t="n">
-        <v>6.923154521083188</v>
+        <v>1.125012609676018</v>
       </c>
       <c r="F4" t="n">
-        <v>9.024405486930508</v>
+        <v>1.466465891626208</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.1832268370743</v>
+        <v>2.629774361024574</v>
       </c>
       <c r="D5" t="n">
-        <v>4.498557836921318</v>
+        <v>0.7310156484997142</v>
       </c>
       <c r="E5" t="n">
-        <v>6.923154521083188</v>
+        <v>1.125012609676018</v>
       </c>
       <c r="F5" t="n">
-        <v>9.024405486930508</v>
+        <v>1.466465891626208</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
